--- a/tabtools/demo/demo_table1.xlsx
+++ b/tabtools/demo/demo_table1.xlsx
@@ -394,7 +394,7 @@
     <t>Table 1. Baseline Characteristics with Balance Diagnostics</t>
   </si>
   <si>
-    <t>No. (Column %), and Mean±SD or Geometric mean (×/GSD), and Median (Q1, Q3)</t>
+    <t>No. (Column %), Mean±SD, Geometric mean (×/GSD), or Median (Q1, Q3)</t>
   </si>
   <si>
     <t>C-reactive protein (mg/L)</t>
@@ -505,7 +505,7 @@
     <t>Table 1. Alternative Formatting Options Demo</t>
   </si>
   <si>
-    <t>Column % (No.), and Mean±SD or Geometric mean (×/GSD), and Median (Q1, Q3)</t>
+    <t>Column % (No.), Mean±SD, Geometric mean (×/GSD), or Median (Q1, Q3)</t>
   </si>
   <si>
     <t>Age at cohort entry (years), mean±SD</t>
@@ -682,7 +682,7 @@
     <t>Table 1. Custom Symbol Formatting Demo</t>
   </si>
   <si>
-    <t>No. (Row %) or No. (Column %), and Mean [SD] or Geometric mean (×/GSD), and Median (Q1 to Q3)</t>
+    <t>No. (Row %), No. (Column %), Mean [SD], Geometric mean (×/GSD), or Median (Q1 to Q3)</t>
   </si>
   <si>
     <t>58.3 [13.4]</t>
@@ -4056,7 +4056,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
-    <col min="2" max="2" width="43.11328125" style="1" customWidth="true"/>
+    <col min="2" max="2" width="40.7109375" style="1" customWidth="true"/>
     <col min="3" max="3" width="12.7109375" style="1" customWidth="true"/>
     <col min="4" max="4" width="12.7109375" style="1" customWidth="true"/>
     <col min="7" max="7" width="10.7109375" style="1" customWidth="true"/>
@@ -5071,7 +5071,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
-    <col min="2" max="2" width="42.51171875" style="1" customWidth="true"/>
+    <col min="2" max="2" width="40.11328125" style="1" customWidth="true"/>
     <col min="3" max="3" width="12.7109375" style="1" customWidth="true"/>
     <col min="4" max="4" width="12.7109375" style="1" customWidth="true"/>
     <col min="5" max="5" width="10.7109375" style="1" customWidth="true"/>
@@ -5390,7 +5390,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
-    <col min="2" max="2" width="48.51171875" style="1" customWidth="true"/>
+    <col min="2" max="2" width="45.7109375" style="1" customWidth="true"/>
     <col min="3" max="3" width="16.7109375" style="1" customWidth="true"/>
     <col min="4" max="4" width="16.7109375" style="1" customWidth="true"/>
     <col min="5" max="5" width="10.7109375" style="1" customWidth="true"/>

--- a/tabtools/demo/demo_table1.xlsx
+++ b/tabtools/demo/demo_table1.xlsx
@@ -839,7 +839,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="18">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -849,34 +849,30 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
-      <b/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
+      <sz val="12"/>
       <name val="Arial"/>
     </font>
     <font>
+      <i/>
       <sz val="8"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="9"/>
       <name val="Arial"/>
-      <i/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="Arial"/>
     </font>
@@ -885,21 +881,16 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <b/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
       <name val="Times New Roman"/>
     </font>
@@ -908,18 +899,8 @@
       <name val="Times New Roman"/>
     </font>
     <font>
+      <b/>
       <sz val="14"/>
-      <name val="Times New Roman"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <b/>
       <name val="Times New Roman"/>
     </font>
   </fonts>
@@ -933,10 +914,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEDF2F9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -946,513 +928,326 @@
     </border>
     <border/>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
+      <right style="thin"/>
+      <top/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
-      <right style="thin"/>
-      <top style="none"/>
+      <right/>
+      <top/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="medium"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="medium"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
-      <right style="none"/>
+      <right/>
       <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="thin"/>
+      <left/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1474,19 +1269,19 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1494,16 +1289,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="15" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1511,16 +1306,16 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1528,16 +1323,16 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="11" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1545,16 +1340,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="7" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1562,16 +1357,16 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="32" t="s">
+      <c r="C6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1579,16 +1374,16 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1596,16 +1391,16 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1613,16 +1408,16 @@
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1630,16 +1425,16 @@
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="32" t="s">
+      <c r="C10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1647,16 +1442,16 @@
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1664,16 +1459,16 @@
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1681,16 +1476,16 @@
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1698,16 +1493,16 @@
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1715,16 +1510,16 @@
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1732,16 +1527,16 @@
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1749,16 +1544,16 @@
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" s="32" t="s">
+      <c r="C17" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1766,16 +1561,16 @@
       <c r="A18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1783,16 +1578,16 @@
       <c r="A19" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1800,16 +1595,16 @@
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1817,16 +1612,16 @@
       <c r="A21" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1834,16 +1629,16 @@
       <c r="A22" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="23" t="s">
+      <c r="B22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="32" t="s">
+      <c r="E22" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1851,16 +1646,16 @@
       <c r="A23" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B23" s="23" t="s">
+      <c r="B23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="8" t="s">
+      <c r="C23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D23" s="8" t="s">
+      <c r="D23" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E23" s="32" t="s">
+      <c r="E23" s="7" t="s">
         <v>75</v>
       </c>
     </row>
@@ -1868,16 +1663,16 @@
       <c r="A24" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="C24" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="D24" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="32" t="s">
+      <c r="E24" s="7" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1885,16 +1680,16 @@
       <c r="A25" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="33" t="s">
+      <c r="D25" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="34" t="s">
+      <c r="E25" s="9" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1921,22 +1716,22 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1944,19 +1739,19 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="70" t="s">
+      <c r="C2" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="D2" s="50" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="E2" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="70" t="s">
+      <c r="F2" s="50" t="s">
         <v>117</v>
       </c>
     </row>
@@ -1964,19 +1759,19 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="11" t="s">
+      <c r="E3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1984,19 +1779,19 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="73" t="s">
+      <c r="C4" s="49" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="73" t="s">
+      <c r="D4" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="73" t="s">
+      <c r="E4" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="73" t="s">
+      <c r="F4" s="49" t="s">
         <v>147</v>
       </c>
     </row>
@@ -2007,16 +1802,16 @@
       <c r="B5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="6" t="s">
         <v>150</v>
       </c>
     </row>
@@ -2027,16 +1822,16 @@
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="8" t="s">
+      <c r="C6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>151</v>
       </c>
     </row>
@@ -2047,16 +1842,16 @@
       <c r="B7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8" t="s">
+      <c r="E7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2067,16 +1862,16 @@
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2087,16 +1882,16 @@
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="E9" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2107,16 +1902,16 @@
       <c r="B10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="6" t="s">
         <v>153</v>
       </c>
     </row>
@@ -2127,16 +1922,16 @@
       <c r="B11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="6" t="s">
         <v>154</v>
       </c>
     </row>
@@ -2147,16 +1942,16 @@
       <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="6" t="s">
         <v>155</v>
       </c>
     </row>
@@ -2164,19 +1959,19 @@
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="72" t="s">
+      <c r="B13" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="74" t="s">
+      <c r="C13" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="74" t="s">
+      <c r="D13" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="74" t="s">
+      <c r="E13" s="48" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="74" t="s">
+      <c r="F13" s="48" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2204,262 +1999,262 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="60" t="s">
         <v>247</v>
       </c>
-      <c r="B1" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="76" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="76" t="s">
+      <c r="B1" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="59" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="85" t="s">
+      <c r="A2" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="85" t="s">
+      <c r="C2" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="85" t="s">
+      <c r="D2" s="58" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="85" t="s">
+      <c r="E2" s="58" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="85" t="s">
+      <c r="F2" s="58" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="84" t="s">
+      <c r="A3" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="84" t="s">
+      <c r="D3" s="57" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="84" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="84" t="s">
+      <c r="E3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="57" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="86" t="s">
+      <c r="A4" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="88" t="s">
+      <c r="C4" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="88" t="s">
+      <c r="D4" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="88" t="s">
+      <c r="E4" s="56" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="88" t="s">
+      <c r="F4" s="56" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="75" t="s">
+      <c r="A5" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="81" t="s">
+      <c r="C5" s="54" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="81" t="s">
+      <c r="E5" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="F5" s="81" t="s">
+      <c r="F5" s="54" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="75" t="s">
+      <c r="A6" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="81" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="81" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="81" t="s">
+      <c r="C6" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="54" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="81" t="s">
+      <c r="F6" s="54" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="75" t="s">
+      <c r="A7" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="81" t="s">
+      <c r="C7" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="81" t="s">
+      <c r="D7" s="54" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="81" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="81" t="s">
+      <c r="E7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="54" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="75" t="s">
+      <c r="A8" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="81" t="s">
+      <c r="C8" s="54" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="81" t="s">
+      <c r="D8" s="54" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="81" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="81" t="s">
+      <c r="E8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="54" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="75" t="s">
+      <c r="A9" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="81" t="s">
+      <c r="C9" s="54" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="81" t="s">
+      <c r="D9" s="54" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="81" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="81" t="s">
+      <c r="E9" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="54" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="75" t="s">
+      <c r="A10" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="81" t="s">
+      <c r="C10" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="81" t="s">
+      <c r="D10" s="54" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="81" t="s">
+      <c r="E10" s="54" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="81" t="s">
+      <c r="F10" s="54" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="75" t="s">
+      <c r="A11" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="81" t="s">
+      <c r="C11" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="81" t="s">
+      <c r="D11" s="54" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="81" t="s">
+      <c r="E11" s="54" t="s">
         <v>75</v>
       </c>
-      <c r="F11" s="81" t="s">
+      <c r="F11" s="54" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="75" t="s">
+      <c r="A12" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="81" t="s">
+      <c r="C12" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="81" t="s">
+      <c r="D12" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="81" t="s">
+      <c r="E12" s="54" t="s">
         <v>76</v>
       </c>
-      <c r="F12" s="81" t="s">
+      <c r="F12" s="54" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="75" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="87" t="s">
+      <c r="A13" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="89" t="s">
+      <c r="C13" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="89" t="s">
+      <c r="D13" s="55" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="89" t="s">
+      <c r="E13" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="F13" s="89" t="s">
+      <c r="F13" s="55" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2487,22 +2282,22 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2510,19 +2305,19 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="15" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2530,19 +2325,19 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="13" t="s">
         <v>257</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2550,19 +2345,19 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C4" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="31" t="s">
+      <c r="C4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>259</v>
       </c>
     </row>
@@ -2570,19 +2365,19 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2590,24 +2385,24 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="23" t="s">
         <v>260</v>
       </c>
       <c r="C7" s="0"/>
@@ -2639,22 +2434,22 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>261</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2662,19 +2457,19 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="15" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2682,19 +2477,19 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="13" t="s">
         <v>263</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2702,19 +2497,19 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C4" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="31" t="s">
+      <c r="C4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>259</v>
       </c>
     </row>
@@ -2722,19 +2517,19 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2742,24 +2537,24 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="E6" s="34" t="s">
+      <c r="E6" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="F6" s="34" t="s">
+      <c r="F6" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="42" t="s">
+      <c r="B7" s="23" t="s">
         <v>260</v>
       </c>
       <c r="C7" s="0"/>
@@ -2791,87 +2586,87 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="71" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="70" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="70" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="20" t="s">
+      <c r="A2" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="69" t="s">
         <v>249</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="68" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="68" t="s">
         <v>256</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="69" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="A3" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="66" t="s">
         <v>267</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="66" t="s">
         <v>267</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="67" t="s">
         <v>268</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="67" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="92" t="s">
+      <c r="A4" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="63" t="s">
         <v>204</v>
       </c>
-      <c r="C4" s="94" t="s">
+      <c r="C4" s="64" t="s">
         <v>255</v>
       </c>
-      <c r="D4" s="94" t="s">
+      <c r="D4" s="64" t="s">
         <v>255</v>
       </c>
-      <c r="E4" s="95" t="s">
+      <c r="E4" s="65" t="s">
         <v>258</v>
       </c>
-      <c r="F4" s="95" t="s">
+      <c r="F4" s="65" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="61" t="s">
         <v>260</v>
       </c>
       <c r="C5" s="0"/>
@@ -2903,22 +2698,22 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2926,19 +2721,19 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="15" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2946,19 +2741,19 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2966,19 +2761,19 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F4" s="11" t="s">
         <v>68</v>
       </c>
     </row>
@@ -2986,19 +2781,19 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="7" t="s">
         <v>69</v>
       </c>
     </row>
@@ -3006,19 +2801,19 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F6" s="32" t="s">
+      <c r="C6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>70</v>
       </c>
     </row>
@@ -3026,19 +2821,19 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3046,19 +2841,19 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3066,19 +2861,19 @@
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3086,19 +2881,19 @@
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E10" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="32" t="s">
+      <c r="C10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="7" t="s">
         <v>71</v>
       </c>
     </row>
@@ -3106,19 +2901,19 @@
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3126,19 +2921,19 @@
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3146,19 +2941,19 @@
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3166,19 +2961,19 @@
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3186,19 +2981,19 @@
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="F15" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3206,19 +3001,19 @@
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F16" s="7" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3226,19 +3021,19 @@
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="F17" s="7" t="s">
         <v>74</v>
       </c>
     </row>
@@ -3246,19 +3041,19 @@
       <c r="A18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="F18" s="34" t="s">
+      <c r="F18" s="9" t="s">
         <v>75</v>
       </c>
     </row>
@@ -3283,16 +3078,16 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3300,13 +3095,13 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="22" t="s">
         <v>46</v>
       </c>
     </row>
@@ -3314,13 +3109,13 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="21" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3328,13 +3123,13 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="20" t="s">
         <v>107</v>
       </c>
     </row>
@@ -3342,13 +3137,13 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="18" t="s">
         <v>81</v>
       </c>
     </row>
@@ -3356,13 +3151,13 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="36" t="s">
+      <c r="D6" s="18" t="s">
         <v>99</v>
       </c>
     </row>
@@ -3370,13 +3165,13 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="36" t="s">
+      <c r="C7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3384,13 +3179,13 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="18" t="s">
         <v>100</v>
       </c>
     </row>
@@ -3398,13 +3193,13 @@
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="D9" s="36" t="s">
+      <c r="D9" s="18" t="s">
         <v>101</v>
       </c>
     </row>
@@ -3412,13 +3207,13 @@
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="D10" s="18" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3426,13 +3221,13 @@
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="36" t="s">
+      <c r="C11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="18" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3440,13 +3235,13 @@
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D12" s="36" t="s">
+      <c r="D12" s="18" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3454,13 +3249,13 @@
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="D13" s="18" t="s">
         <v>109</v>
       </c>
     </row>
@@ -3468,13 +3263,13 @@
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D14" s="36" t="s">
+      <c r="D14" s="18" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3482,13 +3277,13 @@
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="36" t="s">
+      <c r="D15" s="18" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3496,13 +3291,13 @@
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="D16" s="36" t="s">
+      <c r="D16" s="18" t="s">
         <v>103</v>
       </c>
     </row>
@@ -3510,13 +3305,13 @@
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="D17" s="36" t="s">
+      <c r="D17" s="18" t="s">
         <v>104</v>
       </c>
     </row>
@@ -3524,13 +3319,13 @@
       <c r="A18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="D18" s="36" t="s">
+      <c r="D18" s="18" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3538,13 +3333,13 @@
       <c r="A19" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="D19" s="37" t="s">
+      <c r="D19" s="19" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3571,25 +3366,25 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3597,22 +3392,22 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="F2" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="15" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3620,22 +3415,22 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3643,22 +3438,22 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="30" t="s">
+      <c r="C4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="11" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3666,22 +3461,22 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="G5" s="32" t="s">
+      <c r="G5" s="7" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3689,22 +3484,22 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="G6" s="7" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3712,22 +3507,22 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="32" t="s">
+      <c r="C7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3735,22 +3530,22 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="8" t="s">
+      <c r="E8" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="G8" s="32" t="s">
+      <c r="G8" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3758,22 +3553,22 @@
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="E9" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="G9" s="32" t="s">
+      <c r="G9" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3781,22 +3576,22 @@
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="G10" s="32" t="s">
+      <c r="G10" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3804,22 +3599,22 @@
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="32" t="s">
+      <c r="C11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>119</v>
       </c>
     </row>
@@ -3827,22 +3622,22 @@
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="G12" s="32" t="s">
+      <c r="G12" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3850,22 +3645,22 @@
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3873,22 +3668,22 @@
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3896,22 +3691,22 @@
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F15" s="8" t="s">
+      <c r="F15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3919,22 +3714,22 @@
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="F16" s="8" t="s">
+      <c r="F16" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -3942,22 +3737,22 @@
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F17" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="G17" s="32" t="s">
+      <c r="G17" s="7" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3965,22 +3760,22 @@
       <c r="A18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="G18" s="32" t="s">
+      <c r="G18" s="7" t="s">
         <v>118</v>
       </c>
     </row>
@@ -3988,22 +3783,22 @@
       <c r="A19" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="G19" s="32" t="s">
+      <c r="G19" s="7" t="s">
         <v>118</v>
       </c>
     </row>
@@ -4011,27 +3806,27 @@
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D20" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="33" t="s">
+      <c r="E20" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="F20" s="33" t="s">
+      <c r="F20" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="G20" s="34" t="s">
+      <c r="G20" s="9" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="42" t="s">
+      <c r="B21" s="23" t="s">
         <v>120</v>
       </c>
       <c r="C21" s="0"/>
@@ -4066,28 +3861,28 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>121</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="3" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4095,25 +3890,25 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="15" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4121,25 +3916,25 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="21" t="s">
+      <c r="E3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4147,25 +3942,25 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="27" t="s">
         <v>134</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="27" t="s">
         <v>68</v>
       </c>
-      <c r="H4" s="31" t="s">
+      <c r="H4" s="11" t="s">
         <v>147</v>
       </c>
     </row>
@@ -4173,25 +3968,25 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="24" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="D5" s="47" t="s">
+      <c r="D5" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="48" t="s">
+      <c r="E5" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="F5" s="48" t="s">
+      <c r="F5" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="G5" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="H5" s="49" t="s">
+      <c r="H5" s="30" t="s">
         <v>148</v>
       </c>
     </row>
@@ -4199,25 +3994,25 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="G6" s="44" t="s">
+      <c r="G6" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="H6" s="7" t="s">
         <v>149</v>
       </c>
     </row>
@@ -4225,25 +4020,25 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="47" t="s">
+      <c r="D7" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="29" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="49" t="s">
+      <c r="H7" s="30" t="s">
         <v>150</v>
       </c>
     </row>
@@ -4251,25 +4046,25 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="44" t="s">
+      <c r="C8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="F8" s="44" t="s">
+      <c r="F8" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="G8" s="44" t="s">
+      <c r="G8" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="H8" s="32" t="s">
+      <c r="H8" s="7" t="s">
         <v>151</v>
       </c>
     </row>
@@ -4277,25 +4072,25 @@
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="49" t="s">
+      <c r="E9" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="30" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4303,25 +4098,25 @@
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="32" t="s">
+      <c r="E10" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4329,25 +4124,25 @@
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="47" t="s">
+      <c r="D11" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="49" t="s">
+      <c r="E11" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="30" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4355,25 +4150,25 @@
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="44" t="s">
+      <c r="C12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="G12" s="44" t="s">
+      <c r="G12" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="H12" s="32" t="s">
+      <c r="H12" s="7" t="s">
         <v>119</v>
       </c>
     </row>
@@ -4381,25 +4176,25 @@
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="47" t="s">
+      <c r="D13" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="49" t="s">
+      <c r="E13" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="30" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4407,25 +4202,25 @@
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F14" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G14" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="32" t="s">
+      <c r="E14" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4433,25 +4228,25 @@
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="47" t="s">
+      <c r="C15" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="47" t="s">
+      <c r="D15" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="F15" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="49" t="s">
+      <c r="E15" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="30" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4459,25 +4254,25 @@
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="32" t="s">
+      <c r="E16" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4485,25 +4280,25 @@
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="47" t="s">
+      <c r="C17" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="D17" s="47" t="s">
+      <c r="D17" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="49" t="s">
+      <c r="E17" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="30" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4511,25 +4306,25 @@
       <c r="A18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="44" t="s">
+      <c r="E18" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="F18" s="44" t="s">
+      <c r="F18" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="G18" s="44" t="s">
+      <c r="G18" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="7" t="s">
         <v>152</v>
       </c>
     </row>
@@ -4537,25 +4332,25 @@
       <c r="A19" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C19" s="47" t="s">
+      <c r="C19" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="D19" s="47" t="s">
+      <c r="D19" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="E19" s="48" t="s">
+      <c r="E19" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="F19" s="48" t="s">
+      <c r="F19" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="G19" s="48" t="s">
+      <c r="G19" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="H19" s="49" t="s">
+      <c r="H19" s="30" t="s">
         <v>153</v>
       </c>
     </row>
@@ -4563,25 +4358,25 @@
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="G20" s="50" t="s">
+      <c r="G20" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="H20" s="32" t="s">
+      <c r="H20" s="7" t="s">
         <v>154</v>
       </c>
     </row>
@@ -4589,25 +4384,25 @@
       <c r="A21" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D21" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="E21" s="48" t="s">
+      <c r="E21" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="F21" s="48" t="s">
+      <c r="F21" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="G21" s="48" t="s">
+      <c r="G21" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="H21" s="49" t="s">
+      <c r="H21" s="30" t="s">
         <v>155</v>
       </c>
     </row>
@@ -4615,30 +4410,30 @@
       <c r="A22" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="D22" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="E22" s="45" t="s">
+      <c r="E22" s="26" t="s">
         <v>132</v>
       </c>
-      <c r="F22" s="45" t="s">
+      <c r="F22" s="26" t="s">
         <v>144</v>
       </c>
-      <c r="G22" s="45" t="s">
+      <c r="G22" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="H22" s="34" t="s">
+      <c r="H22" s="9" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="23" t="s">
         <v>157</v>
       </c>
       <c r="C23" s="0"/>
@@ -4674,19 +4469,19 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4694,16 +4489,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="15" t="s">
         <v>67</v>
       </c>
     </row>
@@ -4711,16 +4506,16 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>172</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4728,16 +4523,16 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="11" t="s">
         <v>68</v>
       </c>
     </row>
@@ -4745,16 +4540,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="7" t="s">
         <v>145</v>
       </c>
     </row>
@@ -4762,16 +4557,16 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="7" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4779,16 +4574,16 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="7" t="s">
         <v>69</v>
       </c>
     </row>
@@ -4796,16 +4591,16 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="E8" s="32" t="s">
+      <c r="E8" s="7" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4813,16 +4608,16 @@
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="32" t="s">
+      <c r="C9" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>146</v>
       </c>
     </row>
@@ -4830,16 +4625,16 @@
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4847,16 +4642,16 @@
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4864,16 +4659,16 @@
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4881,16 +4676,16 @@
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4898,16 +4693,16 @@
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E14" s="32" t="s">
+      <c r="C14" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>70</v>
       </c>
     </row>
@@ -4915,16 +4710,16 @@
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4932,16 +4727,16 @@
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4949,16 +4744,16 @@
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="C17" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -4966,16 +4761,16 @@
       <c r="A18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="32" t="s">
+      <c r="C18" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4983,16 +4778,16 @@
       <c r="A19" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5000,16 +4795,16 @@
       <c r="A20" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5017,16 +4812,16 @@
       <c r="A21" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B21" s="23" t="s">
+      <c r="B21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="E21" s="32" t="s">
+      <c r="E21" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5034,21 +4829,21 @@
       <c r="A22" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="8" t="s">
         <v>185</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="D22" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="E22" s="34" t="s">
+      <c r="E22" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="42" t="s">
+      <c r="B23" s="23" t="s">
         <v>201</v>
       </c>
       <c r="C23" s="0"/>
@@ -5078,19 +4873,19 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5098,16 +4893,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="15" t="s">
         <v>67</v>
       </c>
     </row>
@@ -5115,16 +4910,16 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5132,16 +4927,16 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="11" t="s">
         <v>68</v>
       </c>
     </row>
@@ -5149,16 +4944,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="7" t="s">
         <v>145</v>
       </c>
     </row>
@@ -5166,16 +4961,16 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="7" t="s">
         <v>146</v>
       </c>
     </row>
@@ -5183,16 +4978,16 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="7" t="s">
         <v>69</v>
       </c>
     </row>
@@ -5200,16 +4995,16 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="32" t="s">
+      <c r="C8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>215</v>
       </c>
     </row>
@@ -5217,16 +5012,16 @@
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>210</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5234,16 +5029,16 @@
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5251,16 +5046,16 @@
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5268,16 +5063,16 @@
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="E12" s="32" t="s">
+      <c r="E12" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5285,16 +5080,16 @@
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E13" s="32" t="s">
+      <c r="C13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>70</v>
       </c>
     </row>
@@ -5302,16 +5097,16 @@
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5319,16 +5114,16 @@
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5336,16 +5131,16 @@
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="23" t="s">
+      <c r="B16" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="C16" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5353,21 +5148,21 @@
       <c r="A17" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="8" t="s">
         <v>209</v>
       </c>
-      <c r="D17" s="33" t="s">
+      <c r="D17" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="E17" s="34" t="s">
+      <c r="E17" s="9" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="23" t="s">
         <v>216</v>
       </c>
       <c r="C18" s="0"/>
@@ -5397,19 +5192,19 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="17" t="s">
         <v>217</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5417,16 +5212,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="15" t="s">
         <v>67</v>
       </c>
     </row>
@@ -5434,16 +5229,16 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5451,16 +5246,16 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="E4" s="31" t="s">
+      <c r="E4" s="11" t="s">
         <v>238</v>
       </c>
     </row>
@@ -5468,16 +5263,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="E5" s="32" t="s">
+      <c r="E5" s="7" t="s">
         <v>239</v>
       </c>
     </row>
@@ -5485,16 +5280,16 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="7" t="s">
         <v>240</v>
       </c>
     </row>
@@ -5502,16 +5297,16 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="6" t="s">
         <v>221</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="E7" s="32" t="s">
+      <c r="E7" s="7" t="s">
         <v>241</v>
       </c>
     </row>
@@ -5519,16 +5314,16 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="32" t="s">
+      <c r="C8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>242</v>
       </c>
     </row>
@@ -5536,16 +5331,16 @@
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="E9" s="32" t="s">
+      <c r="E9" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5553,16 +5348,16 @@
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="E10" s="32" t="s">
+      <c r="E10" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5570,16 +5365,16 @@
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="6" t="s">
         <v>224</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="E11" s="32" t="s">
+      <c r="E11" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5587,16 +5382,16 @@
       <c r="A12" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E12" s="32" t="s">
+      <c r="C12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>243</v>
       </c>
     </row>
@@ -5604,16 +5399,16 @@
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="E13" s="32" t="s">
+      <c r="E13" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5621,16 +5416,16 @@
       <c r="A14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5638,16 +5433,16 @@
       <c r="A15" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="7" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5655,21 +5450,21 @@
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="D16" s="33" t="s">
+      <c r="D16" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="E16" s="34" t="s">
+      <c r="E16" s="9" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="23" t="s">
         <v>244</v>
       </c>
       <c r="C17" s="0"/>
@@ -5701,301 +5496,301 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="45" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="52" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="52" t="s">
+      <c r="B1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="44" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="61" t="s">
+      <c r="A2" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="61" t="s">
+      <c r="C2" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="61" t="s">
+      <c r="D2" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="61" t="s">
+      <c r="E2" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="F2" s="61" t="s">
+      <c r="F2" s="43" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="61" t="s">
+      <c r="G2" s="43" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="60" t="s">
+      <c r="A3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="60" t="s">
+      <c r="D3" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="E3" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="60" t="s">
+      <c r="E3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="62" t="s">
+      <c r="A4" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="64" t="s">
+      <c r="C4" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="64" t="s">
+      <c r="D4" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="64" t="s">
+      <c r="E4" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="F4" s="64" t="s">
+      <c r="F4" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="G4" s="64" t="s">
+      <c r="G4" s="39" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="66" t="s">
+      <c r="A5" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="67" t="s">
+      <c r="C5" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="67" t="s">
+      <c r="D5" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="67" t="s">
+      <c r="E5" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="F5" s="67" t="s">
+      <c r="F5" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="G5" s="67" t="s">
+      <c r="G5" s="40" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="51" t="s">
+      <c r="A6" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="57" t="s">
+      <c r="C6" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="F6" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="G6" s="38" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="66" t="s">
+      <c r="A7" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="67" t="s">
+      <c r="C7" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="67" t="s">
+      <c r="D7" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="67" t="s">
+      <c r="E7" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="40" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="51" t="s">
+      <c r="A8" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="57" t="s">
+      <c r="C8" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="57" t="s">
+      <c r="D8" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="57" t="s">
+      <c r="E8" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="38" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="66" t="s">
+      <c r="A9" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="67" t="s">
+      <c r="C9" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="67" t="s">
+      <c r="D9" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="67" t="s">
+      <c r="E9" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="40" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="51" t="s">
+      <c r="A10" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="57" t="s">
+      <c r="D10" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="57" t="s">
+      <c r="E10" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="F10" s="57" t="s">
+      <c r="F10" s="38" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="57" t="s">
+      <c r="G10" s="38" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="66" t="s">
+      <c r="A11" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="67" t="s">
+      <c r="C11" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="67" t="s">
+      <c r="D11" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="67" t="s">
+      <c r="E11" s="40" t="s">
         <v>132</v>
       </c>
-      <c r="F11" s="67" t="s">
+      <c r="F11" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="67" t="s">
+      <c r="G11" s="40" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="51" t="s">
+      <c r="A12" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="38" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="57" t="s">
+      <c r="D12" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="57" t="s">
+      <c r="E12" s="38" t="s">
         <v>132</v>
       </c>
-      <c r="F12" s="57" t="s">
+      <c r="F12" s="38" t="s">
         <v>76</v>
       </c>
-      <c r="G12" s="57" t="s">
+      <c r="G12" s="38" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="68" t="s">
+      <c r="A13" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="D13" s="69" t="s">
+      <c r="D13" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="69" t="s">
+      <c r="E13" s="41" t="s">
         <v>132</v>
       </c>
-      <c r="F13" s="69" t="s">
+      <c r="F13" s="41" t="s">
         <v>77</v>
       </c>
-      <c r="G13" s="69" t="s">
+      <c r="G13" s="41" t="s">
         <v>156</v>
       </c>
     </row>

--- a/tabtools/demo/demo_table1.xlsx
+++ b/tabtools/demo/demo_table1.xlsx
@@ -20,13 +20,15 @@
     <sheet name="Small Cells Primary" sheetId="12" r:id="rId14"/>
     <sheet name="Small Cells Complement" sheetId="13" r:id="rId15"/>
     <sheet name="Small Cells Binary" sheetId="14" r:id="rId16"/>
+    <sheet name="Small Cells Primary Mode" sheetId="15" r:id="rId17"/>
+    <sheet name="Cell Replace" sheetId="16" r:id="rId18"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1251" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1348" uniqueCount="280">
   <si>
     <t>Table 1. Baseline Characteristics by Treatment Group</t>
   </si>
@@ -106,160 +108,142 @@
     <t>SSRI</t>
   </si>
   <si>
-    <t>N=8,934</t>
-  </si>
-  <si>
-    <t>58.3±13.4</t>
-  </si>
-  <si>
-    <t>5,351 (60)</t>
-  </si>
-  <si>
-    <t>2,333 (26)</t>
-  </si>
-  <si>
-    <t>3,530 (40)</t>
-  </si>
-  <si>
-    <t>3,071 (34)</t>
-  </si>
-  <si>
-    <t>1,778 (20)</t>
-  </si>
-  <si>
-    <t>1,783 (20)</t>
-  </si>
-  <si>
-    <t>1,769 (20)</t>
-  </si>
-  <si>
-    <t>1,786 (20)</t>
-  </si>
-  <si>
-    <t>1,818 (20)</t>
-  </si>
-  <si>
-    <t>1,362 (15)</t>
-  </si>
-  <si>
-    <t>2,764 (31)</t>
-  </si>
-  <si>
-    <t>3,074 (34)</t>
-  </si>
-  <si>
-    <t>1,763 (20)</t>
-  </si>
-  <si>
-    <t>1,333 (15)</t>
-  </si>
-  <si>
-    <t>4,107 (46)</t>
-  </si>
-  <si>
-    <t>4,112 (46)</t>
-  </si>
-  <si>
-    <t>6,079 (68)</t>
-  </si>
-  <si>
-    <t>5,002 (56)</t>
+    <t>N=8,929</t>
+  </si>
+  <si>
+    <t>55.9±13.4</t>
+  </si>
+  <si>
+    <t>5,530 (62)</t>
+  </si>
+  <si>
+    <t>2,280 (26)</t>
+  </si>
+  <si>
+    <t>3,524 (39)</t>
+  </si>
+  <si>
+    <t>3,125 (35)</t>
+  </si>
+  <si>
+    <t>1,727 (19)</t>
+  </si>
+  <si>
+    <t>1,853 (21)</t>
+  </si>
+  <si>
+    <t>1,776 (20)</t>
+  </si>
+  <si>
+    <t>1,758 (20)</t>
+  </si>
+  <si>
+    <t>1,815 (20)</t>
+  </si>
+  <si>
+    <t>1,359 (15)</t>
+  </si>
+  <si>
+    <t>2,755 (31)</t>
+  </si>
+  <si>
+    <t>3,072 (34)</t>
+  </si>
+  <si>
+    <t>1,344 (15)</t>
+  </si>
+  <si>
+    <t>2,566 (29)</t>
+  </si>
+  <si>
+    <t>2,765 (31)</t>
+  </si>
+  <si>
+    <t>5,748 (64)</t>
+  </si>
+  <si>
+    <t>4,629 (52)</t>
   </si>
   <si>
     <t>SNRI</t>
   </si>
   <si>
-    <t>N=6,066</t>
-  </si>
-  <si>
-    <t>58.5±13.3</t>
-  </si>
-  <si>
-    <t>3,621 (60)</t>
-  </si>
-  <si>
-    <t>1,527 (25)</t>
-  </si>
-  <si>
-    <t>2,354 (39)</t>
-  </si>
-  <si>
-    <t>2,185 (36)</t>
-  </si>
-  <si>
-    <t>1,175 (19)</t>
-  </si>
-  <si>
-    <t>1,249 (21)</t>
-  </si>
-  <si>
-    <t>1,228 (20)</t>
-  </si>
-  <si>
-    <t>1,209 (20)</t>
-  </si>
-  <si>
-    <t>1,205 (20)</t>
-  </si>
-  <si>
-    <t>897 (15)</t>
-  </si>
-  <si>
-    <t>1,804 (30)</t>
-  </si>
-  <si>
-    <t>2,162 (36)</t>
-  </si>
-  <si>
-    <t>1,188 (20)</t>
-  </si>
-  <si>
-    <t>912 (15)</t>
-  </si>
-  <si>
-    <t>2,818 (46)</t>
-  </si>
-  <si>
-    <t>2,935 (48)</t>
-  </si>
-  <si>
-    <t>4,148 (68)</t>
-  </si>
-  <si>
-    <t>3,390 (56)</t>
+    <t>N=6,071</t>
+  </si>
+  <si>
+    <t>62.0±12.4</t>
+  </si>
+  <si>
+    <t>3,442 (57)</t>
+  </si>
+  <si>
+    <t>1,580 (26)</t>
+  </si>
+  <si>
+    <t>2,360 (39)</t>
+  </si>
+  <si>
+    <t>2,131 (35)</t>
+  </si>
+  <si>
+    <t>1,226 (20)</t>
+  </si>
+  <si>
+    <t>1,179 (19)</t>
+  </si>
+  <si>
+    <t>1,221 (20)</t>
+  </si>
+  <si>
+    <t>1,237 (20)</t>
+  </si>
+  <si>
+    <t>1,208 (20)</t>
+  </si>
+  <si>
+    <t>900 (15)</t>
+  </si>
+  <si>
+    <t>1,813 (30)</t>
+  </si>
+  <si>
+    <t>2,164 (36)</t>
+  </si>
+  <si>
+    <t>1,193 (20)</t>
+  </si>
+  <si>
+    <t>901 (15)</t>
+  </si>
+  <si>
+    <t>4,359 (72)</t>
+  </si>
+  <si>
+    <t>4,282 (71)</t>
+  </si>
+  <si>
+    <t>4,479 (74)</t>
+  </si>
+  <si>
+    <t>3,763 (62)</t>
   </si>
   <si>
     <t>p-value</t>
   </si>
   <si>
-    <t>0.24</t>
-  </si>
-  <si>
-    <t>0.80</t>
-  </si>
-  <si>
-    <t>0.11</t>
-  </si>
-  <si>
-    <t>0.73</t>
-  </si>
-  <si>
-    <t>0.44</t>
-  </si>
-  <si>
-    <t>0.34</t>
-  </si>
-  <si>
-    <t>0.56</t>
-  </si>
-  <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>0.66</t>
-  </si>
-  <si>
-    <t>0.90</t>
+    <t>&lt;0.001</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>0.22</t>
+  </si>
+  <si>
+    <t>0.51</t>
+  </si>
+  <si>
+    <t>0.41</t>
   </si>
   <si>
     <t>Table 1. Baseline Characteristics (with Total)</t>
@@ -319,10 +303,7 @@
     <t>Effective sample size</t>
   </si>
   <si>
-    <t>ESS=8,928</t>
-  </si>
-  <si>
-    <t>58.4±13.4</t>
+    <t>ESS=5,056</t>
   </si>
   <si>
     <t>60</t>
@@ -349,15 +330,24 @@
     <t>47</t>
   </si>
   <si>
-    <t>ESS=6,058</t>
+    <t>ESS=1,952</t>
+  </si>
+  <si>
+    <t>57.8±13.8</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>Table 1. Crude vs IPTW-Weighted Baseline Characteristics</t>
   </si>
   <si>
@@ -379,13 +369,34 @@
     <t>Weighted SNRI</t>
   </si>
   <si>
+    <t>55</t>
+  </si>
+  <si>
     <t>SMD</t>
   </si>
   <si>
-    <t>0.000</t>
-  </si>
-  <si>
-    <t>0.024</t>
+    <t>0.047</t>
+  </si>
+  <si>
+    <t>0.014</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>0.046</t>
+  </si>
+  <si>
+    <t>0.012</t>
+  </si>
+  <si>
+    <t>0.015</t>
+  </si>
+  <si>
+    <t>0.016</t>
+  </si>
+  <si>
+    <t>0.023</t>
   </si>
   <si>
     <t>Crude and IPTW-weighted statistics shown side-by-side with SMD.</t>
@@ -403,15 +414,15 @@
     <t>Prior hospitalizations</t>
   </si>
   <si>
+    <t>4.4 (×/2.2)</t>
+  </si>
+  <si>
+    <t>2 (1, 3)</t>
+  </si>
+  <si>
     <t>4.5 (×/2.2)</t>
   </si>
   <si>
-    <t>2 (1, 3)</t>
-  </si>
-  <si>
-    <t>4.4 (×/2.2)</t>
-  </si>
-  <si>
     <t>Test</t>
   </si>
   <si>
@@ -430,73 +441,73 @@
     <t>Statistic</t>
   </si>
   <si>
-    <t>t(14998)= -1.16</t>
-  </si>
-  <si>
-    <t>t(14998)=  0.87</t>
-  </si>
-  <si>
-    <t>Z= -0.03</t>
-  </si>
-  <si>
-    <t>Chi2(1)=  0.06</t>
-  </si>
-  <si>
-    <t>Chi2(2)=  4.49</t>
-  </si>
-  <si>
-    <t>Chi2(4)=  2.02</t>
-  </si>
-  <si>
-    <t>Chi2(1)=  0.59</t>
-  </si>
-  <si>
-    <t>Chi2(1)=  0.34</t>
-  </si>
-  <si>
-    <t>Chi2(1)=  8.06</t>
-  </si>
-  <si>
-    <t>Chi2(1)=  0.19</t>
-  </si>
-  <si>
-    <t>Chi2(1)=  0.02</t>
-  </si>
-  <si>
-    <t>0.38</t>
-  </si>
-  <si>
-    <t>0.97</t>
-  </si>
-  <si>
-    <t>0.019</t>
-  </si>
-  <si>
-    <t>0.015</t>
-  </si>
-  <si>
-    <t>0.001</t>
-  </si>
-  <si>
-    <t>0.004</t>
-  </si>
-  <si>
-    <t>0.035</t>
-  </si>
-  <si>
-    <t>0.013</t>
-  </si>
-  <si>
-    <t>0.010</t>
-  </si>
-  <si>
-    <t>0.047</t>
-  </si>
-  <si>
-    <t>0.007</t>
-  </si>
-  <si>
-    <t>0.002</t>
+    <t>t(14998)=-28.47</t>
+  </si>
+  <si>
+    <t>t(14998)= -1.77</t>
+  </si>
+  <si>
+    <t>Z= -1.26</t>
+  </si>
+  <si>
+    <t>Chi2(1)= 41.24</t>
+  </si>
+  <si>
+    <t>Chi2(2)=  0.67</t>
+  </si>
+  <si>
+    <t>Chi2(4)=  5.78</t>
+  </si>
+  <si>
+    <t>Chi2(1)=  0.44</t>
+  </si>
+  <si>
+    <t>Chi2(1)=2696.44</t>
+  </si>
+  <si>
+    <t>Chi2(1)=2271.19</t>
+  </si>
+  <si>
+    <t>Chi2(1)=147.26</t>
+  </si>
+  <si>
+    <t>Chi2(1)=150.79</t>
+  </si>
+  <si>
+    <t>0.077</t>
+  </si>
+  <si>
+    <t>0.21</t>
+  </si>
+  <si>
+    <t>0.477</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>0.018</t>
+  </si>
+  <si>
+    <t>0.107</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>0.011</t>
+  </si>
+  <si>
+    <t>0.954</t>
+  </si>
+  <si>
+    <t>0.862</t>
+  </si>
+  <si>
+    <t>0.204</t>
+  </si>
+  <si>
+    <t>0.206</t>
   </si>
   <si>
     <t>SMD = standardized mean difference. Bold p-values indicate p &lt; 0.05.</t>
@@ -544,91 +555,94 @@
     <t>Marital status, % (No.)</t>
   </si>
   <si>
-    <t>8,934 (59.6)</t>
-  </si>
-  <si>
-    <t>60 (5,351)</t>
-  </si>
-  <si>
-    <t>3 (235)</t>
-  </si>
-  <si>
-    <t>54 (4,857)</t>
-  </si>
-  <si>
-    <t>21 (1,832)</t>
-  </si>
-  <si>
-    <t>15 (1,383)</t>
-  </si>
-  <si>
-    <t>10 (862)</t>
-  </si>
-  <si>
-    <t>26 (2,333)</t>
-  </si>
-  <si>
-    <t>40 (3,530)</t>
-  </si>
-  <si>
-    <t>34 (3,071)</t>
-  </si>
-  <si>
-    <t>31 (2,764)</t>
-  </si>
-  <si>
-    <t>34 (3,074)</t>
-  </si>
-  <si>
-    <t>20 (1,763)</t>
-  </si>
-  <si>
-    <t>15 (1,333)</t>
-  </si>
-  <si>
-    <t>6,066 (40.4)</t>
-  </si>
-  <si>
-    <t>60 (3,621)</t>
-  </si>
-  <si>
-    <t>3 (163)</t>
-  </si>
-  <si>
-    <t>54 (3,299)</t>
-  </si>
-  <si>
-    <t>21 (1,253)</t>
-  </si>
-  <si>
-    <t>16 (942)</t>
-  </si>
-  <si>
-    <t>9 (572)</t>
-  </si>
-  <si>
-    <t>25 (1,527)</t>
-  </si>
-  <si>
-    <t>39 (2,354)</t>
-  </si>
-  <si>
-    <t>36 (2,185)</t>
-  </si>
-  <si>
-    <t>30 (1,804)</t>
-  </si>
-  <si>
-    <t>36 (2,162)</t>
-  </si>
-  <si>
-    <t>20 (1,188)</t>
-  </si>
-  <si>
-    <t>15 (912)</t>
-  </si>
-  <si>
-    <t>0.84</t>
+    <t>8,929 (59.5)</t>
+  </si>
+  <si>
+    <t>62 (5,530)</t>
+  </si>
+  <si>
+    <t>3 (236)</t>
+  </si>
+  <si>
+    <t>54 (4,812)</t>
+  </si>
+  <si>
+    <t>21 (1,842)</t>
+  </si>
+  <si>
+    <t>16 (1,395)</t>
+  </si>
+  <si>
+    <t>10 (880)</t>
+  </si>
+  <si>
+    <t>26 (2,280)</t>
+  </si>
+  <si>
+    <t>39 (3,524)</t>
+  </si>
+  <si>
+    <t>35 (3,125)</t>
+  </si>
+  <si>
+    <t>31 (2,755)</t>
+  </si>
+  <si>
+    <t>34 (3,072)</t>
+  </si>
+  <si>
+    <t>20 (1,758)</t>
+  </si>
+  <si>
+    <t>15 (1,344)</t>
+  </si>
+  <si>
+    <t>6,071 (40.5)</t>
+  </si>
+  <si>
+    <t>57 (3,442)</t>
+  </si>
+  <si>
+    <t>3 (162)</t>
+  </si>
+  <si>
+    <t>55 (3,344)</t>
+  </si>
+  <si>
+    <t>20 (1,243)</t>
+  </si>
+  <si>
+    <t>15 (930)</t>
+  </si>
+  <si>
+    <t>9 (554)</t>
+  </si>
+  <si>
+    <t>26 (1,580)</t>
+  </si>
+  <si>
+    <t>39 (2,360)</t>
+  </si>
+  <si>
+    <t>35 (2,131)</t>
+  </si>
+  <si>
+    <t>30 (1,813)</t>
+  </si>
+  <si>
+    <t>36 (2,164)</t>
+  </si>
+  <si>
+    <t>20 (1,193)</t>
+  </si>
+  <si>
+    <t>15 (901)</t>
+  </si>
+  <si>
+    <t>0.92</t>
+  </si>
+  <si>
+    <t>0.36</t>
   </si>
   <si>
     <t>Yellow rows indicate p &lt; 0.05. Missing values shown as separate category.</t>
@@ -643,37 +657,37 @@
     <t>Rare adverse event</t>
   </si>
   <si>
-    <t>4,857 (60)</t>
-  </si>
-  <si>
-    <t>1,832 (23)</t>
-  </si>
-  <si>
-    <t>1,383 (17)</t>
-  </si>
-  <si>
-    <t>862 (10)</t>
-  </si>
-  <si>
-    <t>235 (3)</t>
-  </si>
-  <si>
-    <t>3,299 (60)</t>
-  </si>
-  <si>
-    <t>1,253 (23)</t>
-  </si>
-  <si>
-    <t>942 (17)</t>
-  </si>
-  <si>
-    <t>572 (9)</t>
-  </si>
-  <si>
-    <t>163 (3)</t>
-  </si>
-  <si>
-    <t>0.99</t>
+    <t>4,812 (60)</t>
+  </si>
+  <si>
+    <t>1,842 (23)</t>
+  </si>
+  <si>
+    <t>1,395 (17)</t>
+  </si>
+  <si>
+    <t>880 (10)</t>
+  </si>
+  <si>
+    <t>236 (3)</t>
+  </si>
+  <si>
+    <t>3,344 (61)</t>
+  </si>
+  <si>
+    <t>1,243 (23)</t>
+  </si>
+  <si>
+    <t>930 (17)</t>
+  </si>
+  <si>
+    <t>554 (9)</t>
+  </si>
+  <si>
+    <t>162 (3)</t>
+  </si>
+  <si>
+    <t>0.61</t>
   </si>
   <si>
     <t>Missing row shows n (%) of missing values per variable.</t>
@@ -685,79 +699,73 @@
     <t>No. (Row %), No. (Column %), Mean [SD], Geometric mean (×/GSD), or Median (Q1 to Q3)</t>
   </si>
   <si>
-    <t>58.3 [13.4]</t>
+    <t>55.9 [13.4]</t>
   </si>
   <si>
     <t>2 (1 to 3)</t>
   </si>
   <si>
-    <t>5,351/8,934 (60)</t>
-  </si>
-  <si>
-    <t>2,333/3,860 (60)</t>
-  </si>
-  <si>
-    <t>3,530/5,884 (60)</t>
-  </si>
-  <si>
-    <t>3,071/5,256 (58)</t>
-  </si>
-  <si>
-    <t>4,857/8,156 (60)</t>
-  </si>
-  <si>
-    <t>1,832/3,085 (59)</t>
-  </si>
-  <si>
-    <t>1,383/2,325 (59)</t>
-  </si>
-  <si>
-    <t>862/1,434 (60)</t>
-  </si>
-  <si>
-    <t>58.5 [13.3]</t>
-  </si>
-  <si>
-    <t>3,621/6,066 (60)</t>
-  </si>
-  <si>
-    <t>1,527/3,860 (40)</t>
-  </si>
-  <si>
-    <t>2,354/5,884 (40)</t>
-  </si>
-  <si>
-    <t>2,185/5,256 (42)</t>
-  </si>
-  <si>
-    <t>3,299/8,156 (40)</t>
-  </si>
-  <si>
-    <t>1,253/3,085 (41)</t>
-  </si>
-  <si>
-    <t>942/2,325 (41)</t>
-  </si>
-  <si>
-    <t>572/1,434 (40)</t>
-  </si>
-  <si>
-    <t>0.244</t>
-  </si>
-  <si>
-    <t>0.382</t>
-  </si>
-  <si>
-    <t>0.974</t>
-  </si>
-  <si>
-    <t>0.805</t>
-  </si>
-  <si>
-    <t>0.106</t>
-  </si>
-  <si>
-    <t>0.973</t>
+    <t>5,530/8,929 (62)</t>
+  </si>
+  <si>
+    <t>2,280/3,860 (59)</t>
+  </si>
+  <si>
+    <t>3,524/5,884 (60)</t>
+  </si>
+  <si>
+    <t>3,125/5,256 (59)</t>
+  </si>
+  <si>
+    <t>4,812/8,156 (59)</t>
+  </si>
+  <si>
+    <t>1,842/3,085 (60)</t>
+  </si>
+  <si>
+    <t>1,395/2,325 (60)</t>
+  </si>
+  <si>
+    <t>880/1,434 (61)</t>
+  </si>
+  <si>
+    <t>62.0 [12.4]</t>
+  </si>
+  <si>
+    <t>3,442/6,071 (57)</t>
+  </si>
+  <si>
+    <t>1,580/3,860 (41)</t>
+  </si>
+  <si>
+    <t>2,360/5,884 (40)</t>
+  </si>
+  <si>
+    <t>2,131/5,256 (41)</t>
+  </si>
+  <si>
+    <t>3,344/8,156 (41)</t>
+  </si>
+  <si>
+    <t>1,243/3,085 (40)</t>
+  </si>
+  <si>
+    <t>930/2,325 (40)</t>
+  </si>
+  <si>
+    <t>554/1,434 (39)</t>
+  </si>
+  <si>
+    <t>&lt;0.0001</t>
+  </si>
+  <si>
+    <t>0.0773</t>
+  </si>
+  <si>
+    <t>0.714</t>
+  </si>
+  <si>
+    <t>0.361</t>
   </si>
   <si>
     <t>SD shown as mean [SD]. IQR uses 'to' separator. Row % for categoricals.</t>
@@ -833,6 +841,33 @@
   </si>
   <si>
     <t>N=100</t>
+  </si>
+  <si>
+    <t>Small-cell suppression: primary mode</t>
+  </si>
+  <si>
+    <t>8 (80)</t>
+  </si>
+  <si>
+    <t>6 (60)</t>
+  </si>
+  <si>
+    <t>8 (40)</t>
+  </si>
+  <si>
+    <t>12 (60)</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Counts from 1 to 4 are shown as &lt;5 without a percentage (primary suppression only: no complementary cells are masked, and other cells, totals and tests are shown as computed). This protects printed counts only.</t>
+  </si>
+  <si>
+    <t>Table 1. cellreplace() Overwrites One Cell</t>
+  </si>
+  <si>
+    <t>Not reported</t>
   </si>
 </sst>
 </file>
@@ -904,7 +939,7 @@
       <name val="Times New Roman"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -914,6 +949,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEDF2F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEBCD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1036,7 +1083,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -1129,12 +1176,48 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom" wrapText="false"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="general" vertical="bottom" wrapText="false"/>
     </xf>
@@ -1159,6 +1242,15 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom" wrapText="false"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
@@ -1183,6 +1275,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom" wrapText="false"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
@@ -1204,6 +1305,15 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="bottom" wrapText="false"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
@@ -1216,19 +1326,43 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="general" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1296,10 +1430,10 @@
         <v>25</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -1313,7 +1447,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>1</v>
@@ -1330,10 +1464,10 @@
         <v>27</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
@@ -1347,10 +1481,10 @@
         <v>28</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1367,7 +1501,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -1381,7 +1515,7 @@
         <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>1</v>
@@ -1398,7 +1532,7 @@
         <v>30</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>1</v>
@@ -1415,7 +1549,7 @@
         <v>31</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>1</v>
@@ -1435,7 +1569,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -1449,7 +1583,7 @@
         <v>32</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>1</v>
@@ -1466,7 +1600,7 @@
         <v>33</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>1</v>
@@ -1483,7 +1617,7 @@
         <v>34</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>1</v>
@@ -1500,7 +1634,7 @@
         <v>35</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>1</v>
@@ -1517,7 +1651,7 @@
         <v>36</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>1</v>
@@ -1534,10 +1668,10 @@
         <v>37</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17">
@@ -1554,7 +1688,7 @@
         <v>1</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
@@ -1568,7 +1702,7 @@
         <v>38</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>1</v>
@@ -1585,7 +1719,7 @@
         <v>39</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>1</v>
@@ -1599,10 +1733,10 @@
         <v>19</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>1</v>
@@ -1616,10 +1750,10 @@
         <v>20</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>1</v>
@@ -1633,13 +1767,13 @@
         <v>21</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23">
@@ -1650,13 +1784,13 @@
         <v>22</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24">
@@ -1667,13 +1801,13 @@
         <v>23</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25">
@@ -1684,13 +1818,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1717,7 +1851,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="17" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
@@ -1739,20 +1873,20 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="68" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="50" t="s">
-        <v>67</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>117</v>
+      <c r="D2" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="68" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="68" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="3">
@@ -1766,7 +1900,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>1</v>
@@ -1779,20 +1913,20 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="62" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="49" t="s">
+      <c r="C4" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="49" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="F4" s="49" t="s">
-        <v>147</v>
+      <c r="D4" s="64" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="F4" s="67" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="5">
@@ -1806,13 +1940,13 @@
         <v>28</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>150</v>
+        <v>67</v>
+      </c>
+      <c r="F5" s="65" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="6">
@@ -1829,10 +1963,10 @@
         <v>1</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7">
@@ -1846,7 +1980,7 @@
         <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" s="6" t="s">
         <v>1</v>
@@ -1866,7 +2000,7 @@
         <v>30</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>1</v>
@@ -1886,7 +2020,7 @@
         <v>31</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>1</v>
@@ -1903,16 +2037,16 @@
         <v>21</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>153</v>
+        <v>67</v>
+      </c>
+      <c r="F10" s="65" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="11">
@@ -1923,16 +2057,16 @@
         <v>22</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>154</v>
+        <v>67</v>
+      </c>
+      <c r="F11" s="65" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="12">
@@ -1943,36 +2077,36 @@
         <v>23</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>155</v>
+        <v>67</v>
+      </c>
+      <c r="F12" s="65" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="61" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="48" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" s="48" t="s">
-        <v>156</v>
+      <c r="C13" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="63" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="63" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="66" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -1999,263 +2133,263 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="60" t="s">
-        <v>247</v>
-      </c>
-      <c r="B1" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="59" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="59" t="s">
+      <c r="A1" s="81" t="s">
+        <v>249</v>
+      </c>
+      <c r="B1" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="80" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="80" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="58" t="s">
+      <c r="A2" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="D2" s="79" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="79" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="79" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="78" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="78" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E3" s="78" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="78" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="71" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="74" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="F2" s="58" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="57" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="57" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="57" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="57" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="53" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="56" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="56" t="s">
+      <c r="F4" s="77" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="69" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="72" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="56" t="s">
+      <c r="E5" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="F5" s="75" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="69" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="F4" s="56" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="51" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="54" t="s">
+      <c r="F6" s="72" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="69" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="72" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="54" t="s">
-        <v>69</v>
-      </c>
-      <c r="F5" s="54" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="54" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="51" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="54" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="54" t="s">
+      <c r="E7" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="69" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="72" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="72" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="54" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="51" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="54" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="54" t="s">
+      <c r="E8" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="72" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="69" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="72" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="54" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="51" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="54" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="54" t="s">
+      <c r="E9" s="72" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="72" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="51" t="s">
+      <c r="A10" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="69" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="72" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="72" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="F10" s="75" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="72" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="54" t="s">
+      <c r="D11" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="54" t="s">
-        <v>74</v>
-      </c>
-      <c r="F10" s="54" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="54" t="s">
+      <c r="E11" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="75" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="72" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="54" t="s">
+      <c r="D12" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="54" t="s">
-        <v>75</v>
-      </c>
-      <c r="F11" s="54" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="54" t="s">
+      <c r="E12" s="72" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="75" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="70" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="73" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="54" t="s">
+      <c r="D13" s="73" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="54" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="54" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="51" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="52" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="55" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="55" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="55" t="s">
-        <v>77</v>
-      </c>
-      <c r="F13" s="55" t="s">
-        <v>156</v>
+      <c r="E13" s="73" t="s">
+        <v>67</v>
+      </c>
+      <c r="F13" s="76" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2283,7 +2417,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="17" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
@@ -2306,19 +2440,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -2329,13 +2463,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>1</v>
@@ -2346,7 +2480,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>1</v>
@@ -2358,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5">
@@ -2366,16 +2500,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>1</v>
@@ -2386,16 +2520,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>1</v>
@@ -2403,7 +2537,7 @@
     </row>
     <row r="7">
       <c r="B7" s="23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
@@ -2435,7 +2569,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
@@ -2458,19 +2592,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -2481,13 +2615,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>1</v>
@@ -2498,7 +2632,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>1</v>
@@ -2510,7 +2644,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5">
@@ -2518,16 +2652,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>1</v>
@@ -2538,16 +2672,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>1</v>
@@ -2555,7 +2689,7 @@
     </row>
     <row r="7">
       <c r="B7" s="23" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C7" s="0"/>
       <c r="D7" s="0"/>
@@ -2586,88 +2720,88 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="71" t="s">
-        <v>266</v>
-      </c>
-      <c r="B1" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="70" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="70" t="s">
+      <c r="A1" s="17" t="s">
+        <v>268</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="69" t="s">
-        <v>249</v>
-      </c>
-      <c r="C2" s="68" t="s">
-        <v>253</v>
-      </c>
-      <c r="D2" s="68" t="s">
-        <v>256</v>
-      </c>
-      <c r="E2" s="69" t="s">
-        <v>79</v>
-      </c>
-      <c r="F2" s="69" t="s">
-        <v>67</v>
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="67" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="66" t="s">
-        <v>267</v>
-      </c>
-      <c r="D3" s="66" t="s">
-        <v>267</v>
-      </c>
-      <c r="E3" s="67" t="s">
-        <v>268</v>
-      </c>
-      <c r="F3" s="67" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="63" t="s">
-        <v>204</v>
-      </c>
-      <c r="C4" s="64" t="s">
-        <v>255</v>
-      </c>
-      <c r="D4" s="64" t="s">
-        <v>255</v>
-      </c>
-      <c r="E4" s="65" t="s">
-        <v>258</v>
-      </c>
-      <c r="F4" s="65" t="s">
-        <v>259</v>
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="82" t="s">
+        <v>208</v>
+      </c>
+      <c r="C4" s="83" t="s">
+        <v>257</v>
+      </c>
+      <c r="D4" s="83" t="s">
+        <v>257</v>
+      </c>
+      <c r="E4" s="84" t="s">
+        <v>260</v>
+      </c>
+      <c r="F4" s="84" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="61" t="s">
-        <v>260</v>
+      <c r="B5" s="23" t="s">
+        <v>262</v>
       </c>
       <c r="C5" s="0"/>
       <c r="D5" s="0"/>
@@ -2680,6 +2814,383 @@
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="F2:F3"/>
     <mergeCell ref="B5:F5"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" style="1" customWidth="true"/>
+    <col min="6" max="6" width="10.7109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="17" t="s">
+        <v>271</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="B7:F7"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="13.7109375" style="1" customWidth="true"/>
+    <col min="5" max="5" width="10.7109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="100" t="s">
+        <v>278</v>
+      </c>
+      <c r="B1" s="99" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="99" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="99" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="99" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="85" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="98" t="s">
+        <v>251</v>
+      </c>
+      <c r="C2" s="97" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="97" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="98" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="85" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="96" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="95" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="95" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="96" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="85" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="88" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="93" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="93" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="94" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="85" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="86" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="89" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="89" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="90" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="85" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="86" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="89" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="89" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="90" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="85" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="86" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="89" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="89" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="90" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="85" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="89" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="90" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="85" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="86" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="89" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="89" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="90" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="85" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="86" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="89" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="89" t="s">
+        <v>59</v>
+      </c>
+      <c r="E10" s="90" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="85" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="86" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="89" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="89" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="90" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="85" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="91" t="s">
+        <v>40</v>
+      </c>
+      <c r="D12" s="91" t="s">
+        <v>279</v>
+      </c>
+      <c r="E12" s="92" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="E2:E3"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -2699,7 +3210,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="17" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
@@ -2728,13 +3239,13 @@
         <v>25</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -2748,10 +3259,10 @@
         <v>26</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>1</v>
@@ -2768,13 +3279,13 @@
         <v>27</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
@@ -2788,13 +3299,13 @@
         <v>28</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -2814,7 +3325,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
@@ -2828,10 +3339,10 @@
         <v>29</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>1</v>
@@ -2848,10 +3359,10 @@
         <v>30</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>1</v>
@@ -2868,10 +3379,10 @@
         <v>31</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>1</v>
@@ -2894,7 +3405,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -2908,10 +3419,10 @@
         <v>32</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>1</v>
@@ -2928,10 +3439,10 @@
         <v>33</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>1</v>
@@ -2948,10 +3459,10 @@
         <v>34</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>1</v>
@@ -2968,10 +3479,10 @@
         <v>35</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>1</v>
@@ -2988,10 +3499,10 @@
         <v>36</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>1</v>
@@ -3008,13 +3519,13 @@
         <v>37</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17">
@@ -3025,16 +3536,16 @@
         <v>21</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18">
@@ -3045,16 +3556,16 @@
         <v>22</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -3079,7 +3590,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="17" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
@@ -3096,13 +3607,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -3116,7 +3627,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -3124,13 +3635,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="D4" s="20" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5">
@@ -3141,10 +3652,10 @@
         <v>3</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6">
@@ -3155,10 +3666,10 @@
         <v>4</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7">
@@ -3183,10 +3694,10 @@
         <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9">
@@ -3197,10 +3708,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
     </row>
     <row r="10">
@@ -3211,10 +3722,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
@@ -3239,10 +3750,10 @@
         <v>10</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -3253,10 +3764,10 @@
         <v>11</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -3267,10 +3778,10 @@
         <v>12</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -3281,10 +3792,10 @@
         <v>13</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16">
@@ -3295,10 +3806,10 @@
         <v>14</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17">
@@ -3309,10 +3820,10 @@
         <v>15</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="18">
@@ -3323,10 +3834,10 @@
         <v>21</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="19">
@@ -3337,10 +3848,10 @@
         <v>22</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
   </sheetData>
@@ -3367,7 +3878,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="17" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
@@ -3396,19 +3907,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="14" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D2" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="E2" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>116</v>
-      </c>
       <c r="G2" s="15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3">
@@ -3422,13 +3933,13 @@
         <v>26</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>26</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>1</v>
@@ -3439,7 +3950,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C4" s="10" t="s">
         <v>1</v>
@@ -3448,10 +3959,10 @@
         <v>1</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>1</v>
@@ -3468,16 +3979,16 @@
         <v>27</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6">
@@ -3491,16 +4002,16 @@
         <v>28</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7">
@@ -3523,7 +4034,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8">
@@ -3537,13 +4048,13 @@
         <v>29</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>1</v>
@@ -3560,13 +4071,13 @@
         <v>30</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>1</v>
@@ -3583,13 +4094,13 @@
         <v>31</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>1</v>
@@ -3615,7 +4126,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12">
@@ -3629,13 +4140,13 @@
         <v>32</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>1</v>
@@ -3652,13 +4163,13 @@
         <v>33</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>1</v>
@@ -3675,13 +4186,13 @@
         <v>34</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>1</v>
@@ -3698,13 +4209,13 @@
         <v>35</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>1</v>
@@ -3721,13 +4232,13 @@
         <v>36</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>1</v>
@@ -3741,19 +4252,19 @@
         <v>21</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18">
@@ -3764,19 +4275,19 @@
         <v>22</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19">
@@ -3787,19 +4298,19 @@
         <v>23</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20">
@@ -3810,24 +4321,24 @@
         <v>24</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C21" s="0"/>
       <c r="D21" s="0"/>
@@ -3862,7 +4373,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="17" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
@@ -3891,25 +4402,25 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" s="33" t="s">
-        <v>128</v>
-      </c>
-      <c r="F2" s="33" t="s">
-        <v>133</v>
-      </c>
-      <c r="G2" s="33" t="s">
-        <v>67</v>
+        <v>45</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>66</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3">
@@ -3923,15 +4434,15 @@
         <v>26</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="38" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="38" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="13" t="s">
@@ -3949,19 +4460,19 @@
         <v>27</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" s="27" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>134</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>147</v>
+        <v>137</v>
+      </c>
+      <c r="G4" s="33" t="s">
+        <v>67</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="5">
@@ -3969,25 +4480,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H5" s="30" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6">
@@ -3995,25 +4506,25 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="G6" s="25" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7">
@@ -4027,19 +4538,19 @@
         <v>28</v>
       </c>
       <c r="D7" s="28" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="G7" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="H7" s="30" t="s">
-        <v>150</v>
+        <v>140</v>
+      </c>
+      <c r="G7" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="H7" s="35" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="8">
@@ -4056,16 +4567,16 @@
         <v>1</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9">
@@ -4079,7 +4590,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E9" s="29" t="s">
         <v>1</v>
@@ -4105,7 +4616,7 @@
         <v>30</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>1</v>
@@ -4131,7 +4642,7 @@
         <v>31</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" s="29" t="s">
         <v>1</v>
@@ -4160,16 +4671,16 @@
         <v>1</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -4183,7 +4694,7 @@
         <v>32</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E13" s="29" t="s">
         <v>1</v>
@@ -4209,7 +4720,7 @@
         <v>33</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>1</v>
@@ -4235,7 +4746,7 @@
         <v>34</v>
       </c>
       <c r="D15" s="28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E15" s="29" t="s">
         <v>1</v>
@@ -4261,7 +4772,7 @@
         <v>35</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>1</v>
@@ -4287,7 +4798,7 @@
         <v>36</v>
       </c>
       <c r="D17" s="28" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E17" s="29" t="s">
         <v>1</v>
@@ -4313,19 +4824,19 @@
         <v>37</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19">
@@ -4336,22 +4847,22 @@
         <v>21</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D19" s="28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F19" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="G19" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="H19" s="30" t="s">
-        <v>153</v>
+        <v>144</v>
+      </c>
+      <c r="G19" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="H19" s="35" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="20">
@@ -4362,22 +4873,22 @@
         <v>22</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E20" s="25" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F20" s="25" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>154</v>
+        <v>67</v>
+      </c>
+      <c r="H20" s="35" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="21">
@@ -4388,22 +4899,22 @@
         <v>23</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F21" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="G21" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="30" t="s">
-        <v>155</v>
+        <v>146</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" s="35" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="22">
@@ -4414,27 +4925,27 @@
         <v>24</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>144</v>
-      </c>
-      <c r="G22" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>156</v>
+        <v>147</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H22" s="36" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="23" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="C23" s="0"/>
       <c r="D23" s="0"/>
@@ -4470,7 +4981,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="17" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
@@ -4490,16 +5001,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -4510,10 +5021,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>1</v>
@@ -4523,17 +5034,17 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>68</v>
+      <c r="D4" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="45" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="5">
@@ -4541,16 +5052,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6">
@@ -4558,33 +5069,33 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>69</v>
+      <c r="B7" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="8">
@@ -4592,16 +5103,16 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9">
@@ -4609,7 +5120,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>1</v>
@@ -4618,7 +5129,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>146</v>
+        <v>204</v>
       </c>
     </row>
     <row r="10">
@@ -4626,13 +5137,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>1</v>
@@ -4643,13 +5154,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>1</v>
@@ -4660,13 +5171,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>1</v>
@@ -4677,13 +5188,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>1</v>
@@ -4694,7 +5205,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>1</v>
@@ -4703,7 +5214,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -4714,10 +5225,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>1</v>
@@ -4731,10 +5242,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>1</v>
@@ -4748,10 +5259,10 @@
         <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>1</v>
@@ -4762,7 +5273,7 @@
         <v>1</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>1</v>
@@ -4771,7 +5282,7 @@
         <v>1</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19">
@@ -4782,10 +5293,10 @@
         <v>17</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>1</v>
@@ -4799,10 +5310,10 @@
         <v>18</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>1</v>
@@ -4816,10 +5327,10 @@
         <v>19</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>1</v>
@@ -4833,10 +5344,10 @@
         <v>20</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>1</v>
@@ -4844,7 +5355,7 @@
     </row>
     <row r="23">
       <c r="B23" s="23" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C23" s="0"/>
       <c r="D23" s="0"/>
@@ -4874,7 +5385,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="17" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
@@ -4894,16 +5405,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -4917,7 +5428,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>1</v>
@@ -4934,10 +5445,10 @@
         <v>27</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5">
@@ -4945,16 +5456,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6">
@@ -4962,16 +5473,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7">
@@ -4985,10 +5496,10 @@
         <v>28</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8">
@@ -4996,7 +5507,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>1</v>
@@ -5005,7 +5516,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9">
@@ -5013,13 +5524,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>1</v>
@@ -5030,13 +5541,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>1</v>
@@ -5047,13 +5558,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>1</v>
@@ -5064,13 +5575,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>1</v>
@@ -5090,7 +5601,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14">
@@ -5104,7 +5615,7 @@
         <v>29</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>1</v>
@@ -5121,7 +5632,7 @@
         <v>30</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>1</v>
@@ -5138,7 +5649,7 @@
         <v>31</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>1</v>
@@ -5149,21 +5660,21 @@
         <v>1</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="23" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C18" s="0"/>
       <c r="D18" s="0"/>
@@ -5193,7 +5704,7 @@
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
       <c r="A1" s="17" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
@@ -5213,16 +5724,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="C2" s="14" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
@@ -5236,7 +5747,7 @@
         <v>26</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>1</v>
@@ -5250,13 +5761,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5">
@@ -5264,16 +5775,16 @@
         <v>1</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6">
@@ -5281,16 +5792,16 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>240</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7">
@@ -5301,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="8">
@@ -5324,7 +5835,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9">
@@ -5335,10 +5846,10 @@
         <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>1</v>
@@ -5352,10 +5863,10 @@
         <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>1</v>
@@ -5369,10 +5880,10 @@
         <v>8</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>1</v>
@@ -5383,7 +5894,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>1</v>
@@ -5392,7 +5903,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13">
@@ -5400,13 +5911,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>1</v>
@@ -5417,13 +5928,13 @@
         <v>1</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>1</v>
@@ -5434,13 +5945,13 @@
         <v>1</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>1</v>
@@ -5451,13 +5962,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>1</v>
@@ -5465,7 +5976,7 @@
     </row>
     <row r="17">
       <c r="B17" s="23" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C17" s="0"/>
       <c r="D17" s="0"/>
@@ -5496,302 +6007,302 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="45" t="s">
-        <v>245</v>
-      </c>
-      <c r="B1" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="44" t="s">
+      <c r="A1" s="60" t="s">
+        <v>247</v>
+      </c>
+      <c r="B1" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="59" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="59" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="43" t="s">
+      <c r="A2" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="58" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="58" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="F2" s="58" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="58" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="57" t="s">
         <v>46</v>
       </c>
-      <c r="E2" s="43" t="s">
-        <v>128</v>
-      </c>
-      <c r="F2" s="43" t="s">
+      <c r="E3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="57" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="51" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="51" t="s">
+        <v>132</v>
+      </c>
+      <c r="F4" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="43" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="42" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="39" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="39" t="s">
+      <c r="G4" s="56" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="52" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="F4" s="39" t="s">
+      <c r="E5" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="F5" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="54" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F6" s="50" t="s">
         <v>68</v>
       </c>
-      <c r="G4" s="39" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="36" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="40" t="s">
+      <c r="G6" s="50" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="52" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="52" t="s">
         <v>49</v>
       </c>
-      <c r="E5" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="F5" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="40" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="F6" s="38" t="s">
-        <v>70</v>
-      </c>
-      <c r="G6" s="38" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="40" t="s">
+      <c r="E7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="52" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="50" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="40" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="38" t="s">
+      <c r="E8" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="52" t="s">
         <v>51</v>
       </c>
-      <c r="E8" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="38" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="40" t="s">
+      <c r="E9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="52" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B10" s="34" t="s">
+      <c r="A10" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="50" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F10" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="54" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="38" t="s">
+      <c r="D11" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" s="40" t="s">
+      <c r="E11" s="52" t="s">
+        <v>135</v>
+      </c>
+      <c r="F11" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="54" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="D12" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="F11" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="40" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B12" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="38" t="s">
+      <c r="E12" s="50" t="s">
+        <v>135</v>
+      </c>
+      <c r="F12" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12" s="54" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="38" t="s">
+      <c r="D13" s="53" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="41" t="s">
-        <v>132</v>
-      </c>
-      <c r="F13" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="41" t="s">
-        <v>156</v>
+      <c r="E13" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="53" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="55" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/tabtools/demo/demo_table1.xlsx
+++ b/tabtools/demo/demo_table1.xlsx
@@ -861,7 +861,7 @@
     <t>0.068</t>
   </si>
   <si>
-    <t>Counts from 1 to 4 are shown as &lt;5 without a percentage (primary suppression only: no complementary cells are masked, and other cells, totals and tests are shown as computed). This protects printed counts only.</t>
+    <t>Counts from 1 to 4 are shown as &lt;5 without a percentage (primary suppression only: no complementary cells are masked). This protects printed counts only.</t>
   </si>
   <si>
     <t>Table 1. cellreplace() Overwrites One Cell</t>
